--- a/PPG/Blogs externos.xlsx
+++ b/PPG/Blogs externos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97FCB3F7-A66D-7049-9826-F90576ACFAB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04FF945C-2C61-7549-937D-258B06F7423E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1060" yWindow="680" windowWidth="27500" windowHeight="16900" xr2:uid="{532D0FCC-2B74-AC48-A173-8BCE0F3E070A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="125">
   <si>
     <t>Publicação</t>
   </si>
@@ -396,6 +396,21 @@
   </si>
   <si>
     <t>https://www.gov.br/hubrasil/pt-br/hospitais-universitarios/regiao-sudeste/huap-uff/comunicacao/noticias/dores-e-cansaco-sao-sinais-de-alerta-para-fibromialgia-e-sindrome-da-fadiga-cronica</t>
+  </si>
+  <si>
+    <t>Burning questions in research</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>https://australian.physio/inmotion/burning-questions-research</t>
+  </si>
+  <si>
+    <t>https://unilavras.edu.br/2026/07/02/nepain-unilavras-encerra-semestre-com-encontro-sobre-pesquisa-ciencia-e-iniciacao-cientifica/</t>
+  </si>
+  <si>
+    <t>NEPAIN UNILAVRAS PROMOVE ENCONTRO SOBRE O PAPEL DA CIÊNCIA E DA PESQUISA NA GRADUAÇÃO</t>
   </si>
 </sst>
 </file>
@@ -768,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9C7B3C5-88EC-8F41-9FD9-49FAABD7FF8A}">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="2" bestFit="1" customWidth="1"/>
@@ -1490,6 +1505,34 @@
       </c>
       <c r="D51" s="3" t="s">
         <v>119</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -1547,6 +1590,8 @@
     <hyperlink ref="D49" r:id="rId47" xr:uid="{E6CB8715-3697-3041-8411-F7A291F77306}"/>
     <hyperlink ref="D50" r:id="rId48" xr:uid="{C54AAE11-E5B4-C947-9FAC-5B7A995F2C11}"/>
     <hyperlink ref="D51" r:id="rId49" xr:uid="{91008C25-8C52-5042-B50B-35E16CD70CC8}"/>
+    <hyperlink ref="D52" r:id="rId50" xr:uid="{419D9C26-BBB2-4546-8C59-0C17A3AD62CA}"/>
+    <hyperlink ref="D53" r:id="rId51" xr:uid="{688CAD15-9661-6647-916B-98E2F8B0356D}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
